--- a/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éric va sur le balcon avec papa. Papa, c'est l'adulte. L'air sent la pluie. Éric reste derrière la protection. La protection est solide sous sa main. Ses pieds restent au sol. Il sent le sol sous les chaussettes. Papa dit : pieds au sol. Derrière la protection. Avec un adulte. Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.</t>
+          <t>Éric va sur le balcon avec papa. Papa, c'est l'adulte. L'air sent la pluie. Éric reste derrière la protection. La protection est solide sous sa main. Ses pieds restent au sol. Il sent le sol sous les chaussettes. Pieds au sol. Derrière la protection. Avec un adulte. Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Éric va sur le balcon avec papa. Papa, c'est l'adulte. L'air sent la pluie. Éric reste derrière la protection. La protection est solide sous sa main. Ses pieds restent au sol. Il sent le sol sous les chaussettes.
+papa|Pieds au sol. Derrière la protection. Avec un adulte.
+narrateur|Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Éric est sur le balcon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Éric a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa ferme la porte. Éric s'assoit près de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Éric est sur le balcon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Éric a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1853,7 @@
           <t>narrateur|Papa ferme la porte. Éric s'assoit près de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éric au balcon avec papa</t>
+          <t>La serviette bleue de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une pince en bois attend. Raphaël aide à étendre la serviette, puis il regarde dehors avec papa, puis avec maman. Pieds au sol, derrière la protection.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éric va sur le balcon avec papa. Papa, c'est l'adulte. L'air sent la pluie. Éric reste derrière la protection. La protection est solide sous sa main. Ses pieds restent au sol. Il sent le sol sous les chaussettes. Pieds au sol. Derrière la protection. Avec un adulte. Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.</t>
+          <t>Une pince en bois dort sur le carrelage. Elle est lisse et un peu ronde. Une serviette bleue sent le savon. La vitre a un peu de buée. Un doigt de Raphaël dessine un rond. Tu as vu la pince, Raphaël ? Elle dormait, papa. On la prend ? Raphaël ramasse la pince. Le bois est tiède dans sa main. En ce moment, papa ouvre le balcon. L'air sent la pluie et le savon. On étend la serviette. On reste avec un adulte. Papa, c'est l'adulte. Pieds au sol. Derrière la protection. Raphaël pose les pieds au sol. Il sent le sol sous les chaussettes. Il reste derrière la protection. La protection est solide sous sa main. Elle est solide, papa. Oui. On reste derrière. Papa tend la serviette bleue. Raphaël donne la pince. La pince fait clic. Bravo. La serviette tient. Raphaël tient le manteau de papa. Il regarde les toits. Un oiseau passe, tout petit. L'oiseau, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Avec un adulte. Bravo. Ils rentrent ensemble. Papa ferme la porte. Plus tard, maman ouvre aussi le balcon. La serviette bleue bouge un peu. On va voir si elle sèche. Pieds au sol. Derrière la protection. Avec un adulte. Raphaël pose encore les pieds au sol. Il reste derrière la protection. Il tient la manche de maman. Elle est presque sèche. Oui. Tu restes avec moi. Bravo, Raphaël. Tu as fait du bon travail. Ils rentrent. Maman ferme la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Éric va sur le balcon avec papa. Papa, c'est l'adulte. L'air sent la pluie. Éric reste derrière la protection. La protection est solide sous sa main. Ses pieds restent au sol. Il sent le sol sous les chaussettes.
-papa|Pieds au sol. Derrière la protection. Avec un adulte.
-narrateur|Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.</t>
+          <t>narrateur|Une pince en bois dort sur le carrelage.
+narrateur|Elle est lisse et un peu ronde.
+narrateur|Une serviette bleue sent le savon.
+narrateur|La vitre a un peu de buée.
+narrateur|Un doigt de Raphaël dessine un rond.
+papa|Tu as vu la pince, Raphaël ?
+enfant-m|Elle dormait, papa.
+papa|On la prend ?
+narrateur|Raphaël ramasse la pince.
+narrateur|Le bois est tiède dans sa main.
+narrateur|En ce moment, papa ouvre le balcon.
+narrateur|L'air sent la pluie et le savon.
+papa|On étend la serviette.
+papa|On reste avec un adulte.
+papa|Papa, c'est l'adulte.
+papa|Pieds au sol.
+papa|Derrière la protection.
+narrateur|Raphaël pose les pieds au sol.
+narrateur|Il sent le sol sous les chaussettes.
+narrateur|Il reste derrière la protection.
+narrateur|La protection est solide sous sa main.
+enfant-m|Elle est solide, papa.
+papa|Oui.
+papa|On reste derrière.
+narrateur|Papa tend la serviette bleue.
+narrateur|Raphaël donne la pince.
+narrateur|La pince fait clic.
+papa|Bravo.
+papa|La serviette tient.
+narrateur|Raphaël tient le manteau de papa.
+narrateur|Il regarde les toits.
+narrateur|Un oiseau passe, tout petit.
+enfant-m|L'oiseau, papa.
+papa|Je le vois.
+papa|Tes pieds au sol ?
+enfant-m|Pieds au sol.
+papa|Avec un adulte.
+papa|Bravo.
+narrateur|Ils rentrent ensemble.
+narrateur|Papa ferme la porte.
+narrateur|Plus tard, maman ouvre aussi le balcon.
+narrateur|La serviette bleue bouge un peu.
+maman|On va voir si elle sèche.
+maman|Pieds au sol.
+maman|Derrière la protection.
+maman|Avec un adulte.
+narrateur|Raphaël pose encore les pieds au sol.
+narrateur|Il reste derrière la protection.
+narrateur|Il tient la manche de maman.
+enfant-m|Elle est presque sèche.
+maman|Oui.
+maman|Tu restes avec moi.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Ils rentrent.
+narrateur|Maman ferme la porte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Éric est sur le balcon. Que fait-il ?</t>
+          <t>Raphaël est sur le balcon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,10 +1571,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Éric est sur le balcon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël est sur le balcon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Éric a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
+          <t>Raphaël a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte. Puis avec maman, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection ? Oui, maman. Bravo. C'est du bon travail. La pince en bois est rentrée. La serviette sent encore le savon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,10 +1747,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Éric a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a gardé les pieds au sol.
+narrateur|Derrière la protection.
+narrateur|Avec papa, l'adulte.
+narrateur|Puis avec maman, l'adulte.
+papa|Tu as gardé les pieds au sol ?
+enfant-m|Oui.
+maman|Derrière la protection ?
+enfant-m|Oui, maman.
+papa|Bravo.
+maman|C'est du bon travail.
+narrateur|La pince en bois est rentrée.
+narrateur|La serviette sent encore le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa ferme la porte. Éric s'assoit près de maman.</t>
+          <t>Raphaël s'assoit près de maman. Ses chaussettes sont un peu froides. La buée a disparu de la vitre. La serviette sèche dehors ? Oui. Et toi, tu es rentré avec nous. Pieds au sol. Derrière la protection. Avec un adulte. Avec papa et maman. Bravo, Raphaël. Raphaël pose la pince sur la table. Le bois fait un petit bruit doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,10 +1925,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa ferme la porte. Éric s'assoit près de maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël s'assoit près de maman.
+narrateur|Ses chaussettes sont un peu froides.
+narrateur|La buée a disparu de la vitre.
+maman|La serviette sèche dehors ?
+enfant-m|Oui.
+papa|Et toi, tu es rentré avec nous.
+papa|Pieds au sol.
+maman|Derrière la protection.
+papa|Avec un adulte.
+enfant-m|Avec papa et maman.
+maman|Bravo, Raphaël.
+narrateur|Raphaël pose la pince sur la table.
+narrateur|Le bois fait un petit bruit doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La serviette bleue sèche au vent. On a mis la pince. Oui. Pieds au sol, derrière la protection. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,10 +2104,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La serviette bleue sèche au vent.
+enfant-m|On a mis la pince.
+papa|Oui.
+maman|Pieds au sol, derrière la protection.
+papa|Bravo, Raphaël.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une pince en bois dort sur le carrelage. Elle est lisse et un peu ronde. Une serviette bleue sent le savon. La vitre a un peu de buée. Un doigt de Raphaël dessine un rond. Tu as vu la pince, Raphaël ? Elle dormait, papa. On la prend ? Raphaël ramasse la pince. Le bois est tiède dans sa main. En ce moment, papa ouvre le balcon. L'air sent la pluie et le savon. On étend la serviette. On reste avec un adulte. Papa, c'est l'adulte. Pieds au sol. Derrière la protection. Raphaël pose les pieds au sol. Il sent le sol sous les chaussettes. Il reste derrière la protection. La protection est solide sous sa main. Elle est solide, papa. Oui. On reste derrière. Papa tend la serviette bleue. Raphaël donne la pince. La pince fait clic. Bravo. La serviette tient. Raphaël tient le manteau de papa. Il regarde les toits. Un oiseau passe, tout petit. L'oiseau, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Avec un adulte. Bravo. Ils rentrent ensemble. Papa ferme la porte. Plus tard, maman ouvre aussi le balcon. La serviette bleue bouge un peu. On va voir si elle sèche. Pieds au sol. Derrière la protection. Avec un adulte. Raphaël pose encore les pieds au sol. Il reste derrière la protection. Il tient la manche de maman. Elle est presque sèche. Oui. Tu restes avec moi. Bravo, Raphaël. Tu as fait du bon travail. Ils rentrent. Maman ferme la porte.</t>
+          <t>Une pince en bois dort sur le carrelage. Elle est lisse et un peu ronde. Une serviette bleue sent le savon. La vitre a un peu de buée. Un doigt de Raphaël dessine un rond. Tu as vu la pince, Raphaël ? Elle dormait, papa. On la prend ? Raphaël ramasse la pince. Le bois est tiède dans sa main. En ce moment, papa ouvre le balcon. L'air sent la pluie et le savon. On étend la serviette. On reste avec un adulte. Papa, c'est l'adulte. Pieds au sol. Derrière la protection. Raphaël pose les pieds au sol. Il sent le sol sous les chaussettes. Il reste derrière la protection. La protection est solide sous sa main. Elle est solide, papa. Oui. On reste derrière. Papa tend la serviette bleue. Raphaël donne la pince. La pince fait clic. Bravo. La serviette tient. Raphaël tient le manteau de papa. Il regarde les toits. Un oiseau passe, tout petit. L'oiseau, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Avec un adulte. Bravo. Ils rentrent ensemble. Papa ferme la porte. Plus tard, maman ouvre aussi le balcon. La serviette bleue bouge un peu. On va voir si elle sèche. Pieds au sol. Derrière la protection. Avec un adulte. Raphaël pose encore les pieds au sol. Il reste derrière la protection. Il tient la manche de maman. Elle est presque sèche. Oui. Tu restes avec moi. Bravo, Raphaël. Ils rentrent. Maman ferme la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éric va sur le balcon avec papa. Papa, c'est l'adulte. L'air sent la pluie. Éric reste derrière la protection. La protection est solide sous sa main. Ses &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol. Il sent le sol sous les chaussettes. Papa dit : pieds au sol. Derrière la protection. Avec un adulte. Éric tient le manteau de papa. Il regarde les toits. Un oiseau passe. Éric garde les pieds au sol. Parce qu'il reste derrière la protection, il peut regarder. Papa sourit. Ils rentrent ensemble. Plus tard, maman ouvre aussi le balcon. Même geste. Éric pose les pieds au sol. Derrière la protection. Avec maman, l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une pince en bois dort sur le carrelage. Elle est lisse et un peu ronde. Une serviette bleue sent le savon. La vitre a un peu de buée. Un doigt de Raphaël dessine un rond. Tu as vu la pince, Raphaël ? Elle dormait, papa. On la prend ? Raphaël ramasse la pince. Le bois est tiède dans sa main. En ce moment, papa ouvre le balcon. L'air sent la pluie et le savon. On étend la serviette. On reste avec un adulte. Papa, c'est l'adulte. Pieds au sol. Derrière la protection. Raphaël pose les pieds au sol. Il sent le sol sous les chaussettes. Il reste derrière la protection. La protection est solide sous sa main. Elle est solide, papa. Oui. On reste derrière. Papa tend la serviette bleue. Raphaël donne la pince. La pince fait clic. Bravo. La serviette tient. Raphaël tient le manteau de papa. Il regarde les toits. Un oiseau passe, tout petit. L'oiseau, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Avec un adulte. Bravo. Ils rentrent ensemble. Papa ferme la porte. Plus tard, maman ouvre aussi le balcon. La serviette bleue bouge un peu. On va voir si elle sèche. Pieds au sol. Derrière la protection. Avec un adulte. Raphaël pose encore les pieds au sol. Il reste derrière la protection. Il tient la manche de maman. Elle est presque sèche. Oui. Tu restes avec moi. Bravo, Raphaël. Ils rentrent. Maman ferme la porte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 maman|Oui.
 maman|Tu restes avec moi.
 maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
 narrateur|Ils rentrent.
 narrateur|Maman ferme la porte.</t>
         </is>
@@ -1416,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éric est sur le balcon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est sur le balcon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1599,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte. Puis avec maman, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection ? Oui, maman. Bravo. C'est du bon travail. La pince en bois est rentrée. La serviette sent encore le savon.</t>
+          <t>Raphaël a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte. Puis avec maman, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection ? Oui, maman. Bravo. La pince en bois est rentrée. La serviette sent encore le savon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éric a gardé les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Derrière la protection. Avec papa, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte. Puis avec maman, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection ? Oui, maman. Bravo. La pince en bois est rentrée. La serviette sent encore le savon.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,7 +1755,6 @@
 maman|Derrière la protection ?
 enfant-m|Oui, maman.
 papa|Bravo.
-maman|C'est du bon travail.
 narrateur|La pince en bois est rentrée.
 narrateur|La serviette sent encore le savon.</t>
         </is>
@@ -1790,7 +1788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Papa ferme la porte. Éric s'assoit près de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël s'assoit près de maman. Ses chaussettes sont un peu froides. La buée a disparu de la vitre. La serviette sèche dehors ? Oui. Et toi, tu es rentré avec nous. Pieds au sol. Derrière la protection. Avec un adulte. Avec papa et maman. Bravo, Raphaël. Raphaël pose la pince sur la table. Le bois fait un petit bruit doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1964,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La serviette bleue sèche au vent. On a mis la pince. Oui. Pieds au sol, derrière la protection. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>La serviette bleue sèche au vent. On a mis la pince. Oui. Pieds au sol, derrière la protection. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La serviette bleue sèche au vent. On a mis la pince. Oui. Pieds au sol, derrière la protection. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,8 +2106,7 @@
 enfant-m|On a mis la pince.
 papa|Oui.
 maman|Pieds au sol, derrière la protection.
-papa|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Raphaël.</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Éric, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
